--- a/AAII_Financials/Quarterly/RVTY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVTY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>RVTY</t>
   </si>
@@ -656,296 +656,308 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46208</v>
+      </c>
+      <c r="E7" s="2">
         <v>46117</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46019</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45655</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45018</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44927</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44836</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44745</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44654</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44563</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44472</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44381</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>729700</v>
+      </c>
+      <c r="E8" s="3">
         <v>711100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>772100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>698900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>720300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>664800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>729400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>684000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>691700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>649900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>695900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>670700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>709100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>674900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>741200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>711800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>895600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>963200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1027900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>861300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1228500</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>312800</v>
+      </c>
+      <c r="E9" s="3">
         <v>323500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>350400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>324300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>327700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>289200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>317700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>299000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>306000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>294700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>314900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>297400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>306700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>292600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>304900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>304800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>343900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>368400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>384100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>338500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>543300</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>416900</v>
+      </c>
+      <c r="E10" s="3">
         <v>387700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>421700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>374600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>392600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>375500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>411700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>385000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>385700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>355200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>381000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>373300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>402300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>382300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>436300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>407000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>551700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>594800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>643800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>522800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>685200</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -969,73 +981,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E12" s="3">
         <v>57900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>58200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>50800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>53300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>53600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>51300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>48400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>47400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>49700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>53100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>51800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>56100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>55500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>54500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>53500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>56000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>57500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>60600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>49400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>65800</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1099,118 +1115,124 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E14" s="3">
         <v>15900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>41800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>20800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>12700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>26500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>31700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>68400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>37700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>34300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>19000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>24900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>28100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-2200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>71900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>15700</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E15" s="3">
         <v>105100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>103100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>102100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>102800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>97400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>105000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>107700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>107300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>107800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>105600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>108300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>108900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>109000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1229,8 +1251,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1251,138 +1276,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>605300</v>
+      </c>
+      <c r="E17" s="3">
         <v>623300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>617100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>602600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>617200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>583600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>592900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>582700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>587400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>576800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>609500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>577900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>601000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>579100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>603700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>601000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>663100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>701200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>728100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>665800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>896000</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>124400</v>
+      </c>
+      <c r="E18" s="3">
         <v>87900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>154900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>96400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>103100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>81200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>136500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>101400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>104300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>73100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>86400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>92800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>108000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>95700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>137500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>110800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>232500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>262000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>299800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>195500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>332500</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1406,333 +1438,349 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-19600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>29800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>23500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>27600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-17000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>225100</v>
+      </c>
+      <c r="E21" s="3">
         <v>189400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>254200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>194400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>202000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>175400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>239000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>207800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>210900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>178400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>211500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>198600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>215700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>174900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>265200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>191400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>352900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>373300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>452500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>265700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>418400</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E22" s="3">
         <v>24700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>23500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>23000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>26000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>22700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>22500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>25900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>27100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>28400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>27700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>43500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E23" s="3">
         <v>50000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>91600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>55700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>68700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>52400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>94600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>100400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>86700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>34500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>50600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>71600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>29400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>138400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>82100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>206300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>224900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>299700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>135000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>326100</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E24" s="3">
         <v>9100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-32200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>41000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>44700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>40800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>115600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>27400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>80100</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1796,138 +1844,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E26" s="3">
         <v>40900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>95800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>47200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>55200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>41700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>88400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>93400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>72600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>28700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>63600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>32500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>58600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>97500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>69500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>161600</v>
-      </c>
-      <c r="T26" s="3">
-        <v>184100</v>
       </c>
       <c r="U26" s="3">
         <v>184100</v>
       </c>
       <c r="V26" s="3">
+        <v>184100</v>
+      </c>
+      <c r="W26" s="3">
         <v>107600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>246000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E27" s="3">
         <v>40700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>98400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>46700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>53900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>42200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>94600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>94400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>55400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>78600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>569500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>97500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>69500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>161600</v>
-      </c>
-      <c r="T27" s="3">
-        <v>184100</v>
       </c>
       <c r="U27" s="3">
         <v>184100</v>
       </c>
       <c r="V27" s="3">
+        <v>184100</v>
+      </c>
+      <c r="W27" s="3">
         <v>107600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>246000</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1991,73 +2048,79 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E29" s="3">
         <v>-200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>2600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-600</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-1300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>6300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-17200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-2700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>15000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-23000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-23100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>544600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>30200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>15800</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>28100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-7100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>6100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>20100</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2121,8 +2184,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2186,138 +2252,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>19600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-29800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-23500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-27600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>17000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-10300</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E33" s="3">
         <v>40700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>98400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>46700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>53900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>42200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>94600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>94400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>55400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>78600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>569500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>127700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>85300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>189700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>176900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>190200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>127700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>245900</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2381,143 +2456,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E35" s="3">
         <v>40700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>98400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>46700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>53900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>42200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>94600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>94400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>55400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>78600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>569500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>127700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>85300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>189700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>176900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>190200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>127700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>245900</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46208</v>
+      </c>
+      <c r="E38" s="2">
         <v>46117</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46019</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45655</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45018</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44927</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44836</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44745</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44654</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44563</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44472</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44381</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2541,8 +2625,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2566,73 +2651,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1022900</v>
+      </c>
+      <c r="E41" s="3">
         <v>860300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>919900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>931400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>991800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1137600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1163400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1229800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1248100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>998100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>913200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1136700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1331900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2267200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>454400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>360900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>669800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>618300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>487400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>572800</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2658,25 +2747,25 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>706100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>697300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>689900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>293000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>739100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>194000</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>10</v>
@@ -2696,279 +2785,294 @@
       <c r="W42" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>709200</v>
+      </c>
+      <c r="E43" s="3">
         <v>691400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>744700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>680300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>661100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>617400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>632400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>602100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>597400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>589000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>632800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>644600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>626900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>586900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>612800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>540900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>932100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>941700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1023800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>947800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>992600</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>378500</v>
+      </c>
+      <c r="E44" s="3">
         <v>387500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>379500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>379900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>388500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>381300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>367600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>404600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>401400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>414000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>428100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>435700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>436800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>429400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>405500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>378300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>624300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>645900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>624700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>645400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>513400</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>186400</v>
+      </c>
+      <c r="E45" s="3">
         <v>188700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>195700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>151000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>193600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>180500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>185200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>210900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>204300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>359500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>335900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>402000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>387600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>317100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1816000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1796600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>190500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>197100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>174000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>170200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>181200</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2297700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2128300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2239700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2143800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2236200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2317900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2349600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2448400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3158700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3059300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3001100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2913200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3523300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3795600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3288600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3116500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2107800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2454500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2440800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2250800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2260000</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3">
         <v>90000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -2976,11 +3080,11 @@
       <c r="H47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3">
         <v>95300</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>10</v>
@@ -2988,11 +3092,11 @@
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N47" s="3">
         <v>82800</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>10</v>
@@ -3000,8 +3104,8 @@
       <c r="P47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3021,138 +3125,147 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>607200</v>
+      </c>
+      <c r="E48" s="3">
         <v>628900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>644700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>668200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>676200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>660400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>649900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>667200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>646900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>652700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>664700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>645900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>658000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>659100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>671300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>620500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>743000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>749000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>753400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>746400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>587600</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8831800</v>
+      </c>
+      <c r="E49" s="3">
         <v>8917300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8960500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9026600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9129400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9082900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9104500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9321900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9322500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9423000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9555900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9555400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9715600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9800600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9858900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9774500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11014700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11310200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11479700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11581000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5405600</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3216,8 +3329,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3281,73 +3397,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>276900</v>
+      </c>
+      <c r="E52" s="3">
         <v>289800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>300400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>321100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>299600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>187500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>332200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>296800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>297600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>252000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>307000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>321600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>382900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>311100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>312300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>324200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>334800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>326700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>321700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>486300</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3411,73 +3533,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12045800</v>
+      </c>
+      <c r="E54" s="3">
         <v>11996600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12168400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12139000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12362800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12360700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12392500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12769700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13424800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13432700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13564700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13421500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14218500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14638200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14129900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13823800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14189700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14848500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15000600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14899800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8739500</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3501,8 +3629,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3526,398 +3655,417 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>165700</v>
+      </c>
+      <c r="E57" s="3">
         <v>169700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>185500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>175800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>178200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>178100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>167500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>176400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>174900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>183500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>204100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>188300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>235700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>266900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>272800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>275800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>333700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>376700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>355500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>320400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>324700</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>572200</v>
+      </c>
+      <c r="E58" s="3">
         <v>575800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>618900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>583800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
       </c>
       <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
         <v>23800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>711400</v>
       </c>
       <c r="L58" s="3">
         <v>711400</v>
       </c>
       <c r="M58" s="3">
+        <v>711400</v>
+      </c>
+      <c r="N58" s="3">
         <v>754800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>727500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>478900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>479400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>470900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>503500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>204900</v>
+      </c>
+      <c r="E59" s="3">
         <v>206700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>240800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>214600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>27500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>223700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>33300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>800700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>706400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>705900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>882600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>854000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>820100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>793400</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1276400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1238600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1331200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1222700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>671800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>648200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>653100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>687900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1390000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1374200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1450500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1447800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1366800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1563700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1544500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1485700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1043800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1263100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1213700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1145000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1122800</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2769400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2774300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2779300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2785200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3374600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3325100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3302000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3314100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3285700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3292200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3310500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3286400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4027900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4030400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3923300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3898300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4484300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4864000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4979700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5099100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2348500</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E62" s="3">
         <v>21000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>195900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>14200</v>
       </c>
       <c r="G62" s="3">
         <v>14200</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H62" s="3">
+        <v>14200</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>195300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>220200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1279100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1374600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1494400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1535100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1665800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1697200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1028300</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3981,8 +4129,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4046,8 +4197,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4111,73 +4265,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4817100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4813900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4918100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4763100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4806600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4723600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4725600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4848000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5554500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5586200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5691900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5727300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6348600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6604300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6747000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6758600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7022600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7662100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7859300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7941300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4499700</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4201,8 +4361,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4266,8 +4427,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4331,8 +4495,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4396,8 +4563,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4461,73 +4631,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6131200</v>
+      </c>
+      <c r="E72" s="3">
         <v>6087200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6054300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5963800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5925100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5879200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5845200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5759100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5673300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5626600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5609200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5539400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5538500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5511700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4951000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4834000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4756600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4585200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4417200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4235800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4116800</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4591,8 +4767,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4656,8 +4835,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4721,73 +4903,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7228800</v>
+      </c>
+      <c r="E76" s="3">
         <v>7182700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7250400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7375900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7556200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7637100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7666900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7921700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7870300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7846500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7872700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7694300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7870000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8033800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7382900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7065200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7167200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7186300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7141200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6958600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4239800</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4851,143 +5039,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46208</v>
+      </c>
+      <c r="E80" s="2">
         <v>46117</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46019</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45655</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45018</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44927</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44836</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44745</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44654</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44563</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44472</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44381</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E81" s="3">
         <v>40700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>98400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>46700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>53900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>42200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>94600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>94400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>55400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>78600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>569500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>127700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>85300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>189700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>176900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>190200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>127700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>245900</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5011,73 +5208,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E83" s="3">
         <v>14700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>15000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>104200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>83300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>119400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>120100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>125100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>87100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>75600</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5141,8 +5342,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5206,8 +5410,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5271,8 +5478,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5336,8 +5546,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5401,73 +5614,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>191900</v>
+      </c>
+      <c r="E89" s="3">
         <v>115200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>182000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>138500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>134300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>128200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>174200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>147900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>158600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>147600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>196600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-33500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-135300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>63500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>139200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>160000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>97500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>283200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>335600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>313800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>287900</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5491,73 +5710,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-23200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-29400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-32400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-32800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-20400</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5621,8 +5844,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5686,73 +5912,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-78300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-20500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>19000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>690200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>121500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-18200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-414800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>434900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-571000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1864500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-25700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-28400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-56300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-60000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3300900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-290000</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5776,8 +6008,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5785,22 +6018,22 @@
         <v>7800</v>
       </c>
       <c r="E96" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F96" s="3">
         <v>8000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>8100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>8300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>8400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>8500</v>
-      </c>
-      <c r="J96" s="3">
-        <v>8600</v>
       </c>
       <c r="K96" s="3">
         <v>8600</v>
@@ -5812,16 +6045,16 @@
         <v>8600</v>
       </c>
       <c r="N96" s="3">
+        <v>8600</v>
+      </c>
+      <c r="O96" s="3">
         <v>8700</v>
-      </c>
-      <c r="O96" s="3">
-        <v>8800</v>
       </c>
       <c r="P96" s="3">
         <v>8800</v>
       </c>
       <c r="Q96" s="3">
-        <v>-8800</v>
+        <v>8800</v>
       </c>
       <c r="R96" s="3">
         <v>-8800</v>
@@ -5836,13 +6069,16 @@
         <v>-8800</v>
       </c>
       <c r="V96" s="3">
-        <v>-7800</v>
+        <v>-8800</v>
       </c>
       <c r="W96" s="3">
         <v>-7800</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>-7800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5906,8 +6142,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5971,8 +6210,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6036,199 +6278,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-88900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-176300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-215100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-302500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-163700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-193000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-873700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-26500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-35000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-19600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-586000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-228300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-113200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-76700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-65600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-354600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-164900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-139000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2755400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-257700</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E101" s="3">
         <v>16100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-30300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>17100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>17700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-17400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-23300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>17700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-17400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-23300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-10600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-5900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>162700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-59600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-60400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-145700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-66400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>250000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>85100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-223600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-195400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-935200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1797800</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>54400</v>
       </c>
       <c r="R102" s="3">
         <v>54400</v>
       </c>
       <c r="S102" s="3">
+        <v>54400</v>
+      </c>
+      <c r="T102" s="3">
         <v>-308800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>51400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>130300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-237600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-263700</v>
       </c>
     </row>
